--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.8.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.8.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.8" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00138_18940629.8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.8.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -975,7 +975,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.8.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.8.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00138_18940629.8" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y98"/>
+  <dimension ref="A1:Y94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -613,19 +613,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Among those to whom the ladies wer Ã©</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The P. P. Aâ€™s. or Amoreans held an ex-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES,</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES,</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -646,13 +650,13 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L1177: line starts with punctuation glued to text :: ** 6 20 per cent.</t>
+          <t>L771: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | abbreviation/spacing may be garbled :: •5.30 and 900 p.m. A</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | missing space around punctuation :: Anâ€™ set 'em in the settinâ€™ room,because,</t>
+          <t>L73: missing space around punctuation :: An’ set 'em in the settin’ room,because,</t>
         </is>
       </c>
       <c r="V2" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -700,19 +704,19 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Read Mr. George Cline's advertise-</t>
+          <t>L168: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: fl FAIR MAIDENâ€™S NO</t>
+          <t>L412: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L168: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -733,7 +737,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L1231: symbol-only separator/garbage line | line starts with punctuation glued to text :: ***** 70</t>
+          <t>L776: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •Calls at Oakvil’e.</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -741,7 +745,7 @@
       <c r="V3" s="1" t="inlineStr"/>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>L771: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | abbreviation/spacing may be garbled :: â€¢5.30 and 900 p.m. A</t>
+          <t>L771: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | abbreviation/spacing may be garbled :: •5.30 and 900 p.m. A</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr"/>
@@ -783,12 +787,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a room should be cool but not chilling â€”</t>
+          <t>L512: stray/suspicious non-ASCII glyph(s): U+5C0F CJK UNIFIED IDEOGRAPH-5C0F | isolated marker/symbol line :: 小</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: But we canâ€™t take no chances, anâ€™ the</t>
+          <t>L698: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: '• De Koven’s Nita Gitana" in a</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -816,7 +820,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L1301: line starts with digit/letter garbage token | suspicious token(s): 1further (letter/digit mix) :: 1further</t>
+          <t>L1177: line starts with punctuation glued to text :: ** 6 20 per cent.</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -834,12 +838,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>127</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>161</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -862,12 +866,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” The Sons of England band and its</t>
+          <t>L739: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: he's a-stayinâ€™ here.</t>
+          <t>L771: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | abbreviation/spacing may be garbled :: •5.30 and 900 p.m. A</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -893,7 +897,11 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L1231: symbol-only separator/garbage line | line starts with punctuation glued to text :: ***** 70</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -933,12 +941,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Byron C. Hall, Deputy Supreme Or-</t>
+          <t>L852: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: I think we'd also better get a spinninâ€™</t>
+          <t>L776: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •Calls at Oakvil’e.</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -964,7 +972,11 @@
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L1301: line starts with digit/letter garbage token | suspicious token(s): 1further (letter/digit mix) :: 1further</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1002,14 +1014,10 @@
           <t>L782: suspicious token(s): 40c (letter/digit mix) :: and return, 40c. Tickets good going June 30th</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | missing space around punctuation :: Anâ€™ set 'em in the settinâ€™ room,because,</t>
+          <t>L1415: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • BAILIFF'S SALE.</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1021,7 +1029,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L412: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -1031,7 +1039,11 @@
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L1415: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • BAILIFF'S SALE.</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr"/>
@@ -1069,21 +1081,13 @@
           <t>L802: suspicious token(s): TheImperi (odd internal casing) :: TheImperi</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L166: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pany and all concerned,â€” We, the mem-</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L74: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 'tween me anâ€™ you.</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L512: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å°�</t>
+          <t>L512: stray/suspicious non-ASCII glyph(s): U+5C0F CJK UNIFIED IDEOGRAPH-5C0F | isolated marker/symbol line :: 小</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1136,16 +1140,8 @@
           <t>L814: suspicious token(s): DENIun (odd internal casing) :: fleet vases of Benares brass, and hand- DENIun</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Anâ€™, by the way, ye'd better buy, say</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1181,12 +1177,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1203,16 +1199,8 @@
           <t>L876: suspicious token(s): 95c (letter/digit mix) :: $1 ; $1.50 white quilts reduced to 95c.;</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Andrew Fox, No. 55 Oxford street,</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: They does â€™em up in lime these days, an'</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1253,7 +1241,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1270,16 +1258,8 @@
           <t>L877: suspicious token(s): 4c (letter/digit mix), 50c (letter/digit mix) :: flannelette, 4 3-4c. a yard ; 50c. dress .</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: stand on either side of the fireplace â€”</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sells â€™em out in kegs,</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1315,7 +1295,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1337,16 +1317,8 @@
           <t>L878: suspicious token(s): 25c (letter/digit mix), 75c (letter/digit mix) :: materials reduced to 25c.; 75c. dress</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L465: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 181 tons nut â€” all best Scranton, 441 tons Rey-</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Then every morninâ€™ Iâ€™ll go out and sort</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1404,16 +1376,8 @@
           <t>L879: suspicious token(s): 2c (letter/digit mix) :: materials reduced to 87 1-2c. a yard ;</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L509: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” James McClemont, laborer, of Erie</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The coons and haylofts, where theyâ€™re</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1454,7 +1418,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1471,16 +1435,8 @@
           <t>L880: suspicious token(s): 2c (letter/digit mix) :: best wool delaines, 19 1-2c. a yard,</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L512: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å°�</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: found â€˜emâ€”anâ€˜, I say,</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1538,16 +1494,8 @@
           <t>L881: suspicious token(s): 2c (letter/digit mix) :: worth 37 1-2c.; one hundred dress lengths</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L622: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” A foundationless report appeared in</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: It makes me laugh to think of â€™em. They</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1605,16 +1553,8 @@
           <t>L882: suspicious token(s): 40c (letter/digit mix) :: of best sateens, worth 35 to 40c. a yard,</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: call us "new" anâ€™ "green,"</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1672,16 +1612,8 @@
           <t>L883: suspicious token(s): 2c (letter/digit mix) :: your choice of the lot for 12 1-2c. a</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: But theyâ€™re the very verdantest that</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1727,16 +1659,8 @@
           <t>L888: suspicious token(s): IRose (odd internal casing) :: IRose of England Lodge, No. 119, S.</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L867: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦ New York</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Harper's Bazar.</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1782,16 +1706,8 @@
           <t>L898: suspicious token(s): 6TM (letter/digit mix) :: FRIDAY, 6TM JULY NEXT,</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Stuttgart.â€¦</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L205: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A Resort in Oneâ€™s Own Houseâ€”How to</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1837,16 +1753,8 @@
           <t>L922: suspicious token(s): 1odges (letter/digit mix) :: Mem bers of si ster 1odges a rein vited to attend.</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦. Bremen</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Church in Harperâ€™s Bazar, is the entire</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1892,16 +1800,8 @@
           <t>L1301: line starts with digit/letter garbage token | suspicious token(s): 1further (letter/digit mix) :: 1further</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L905: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a room should be cool but not chillingâ€”</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -1947,16 +1847,8 @@
           <t>L1352: suspicious token(s): an0 (letter/digit mix) :: an0</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L261: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: effect, yet as a generalâ€™thing this treat-</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -2002,16 +1894,8 @@
           <t>L1392: suspicious token(s): 78p (letter/digit mix) :: Yesterday, 6 p. m., 78p: to-day, 9 a. m.,</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L915: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: suggestion of pistache, that loveliest â€˜of</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -2053,16 +1937,8 @@
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L923: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L275: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: goldâ€”are equally charming. If the ceil-</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -2104,16 +1980,8 @@
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L924: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L303: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: at Queenston with "Chippewa," â€œCibola" and</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -2155,16 +2023,8 @@
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L930: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 18 buta minuteâ€™s walk from the Grand Trunk</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2206,16 +2066,8 @@
         </is>
       </c>
       <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L931: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Queenston Heights, Brockâ€™s Monument, The</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
@@ -2254,11 +2106,7 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L328: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Read the " Times"â€”only twenty-five</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
@@ -2297,11 +2145,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Dummy excursion to Dundas and</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
@@ -2340,11 +2184,7 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L335: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN :: â€”A. H. Cumming had a sÃ©t of harness</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
@@ -2383,11 +2223,7 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”William Hutton, No. 347 Victoria</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
@@ -2426,11 +2262,7 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Received this week, three cases very</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
@@ -2446,7 +2278,7 @@
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>L1175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Farmersâ€™ L. &amp; Svs..........</t>
+          <t>L1175: punctuation artifact: repeated periods :: Farmers’ L. &amp; Svs..........</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2469,11 +2301,7 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: latest styles in straw hats at Waughâ€™s,</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
@@ -2512,11 +2340,7 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L347: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”A big slaughter sale of warm weather</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
@@ -2555,11 +2379,7 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Subscribe Tor the " Times" and get</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
@@ -2598,11 +2418,7 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: all the news of the dayâ€”twenty-five</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
@@ -2641,11 +2457,7 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L355: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Miss Lettie Legate, matron of the</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
@@ -2684,11 +2496,7 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L362: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: your care be for the work itself.â€”Spur-</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
@@ -2727,11 +2535,7 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
@@ -2770,11 +2574,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L414: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Read Mr. George Cline's</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
@@ -2813,11 +2613,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: dian W heelmenâ€™s Meet, and the Domi ion Pro-</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
@@ -2856,11 +2652,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L444: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: apply to any of the companyâ€™s agents.</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
@@ -2899,16 +2691,12 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L451: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”" Evangelist " Belleville was brought</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L732: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
@@ -2942,11 +2730,7 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L461: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”The full summer train service between</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
@@ -2985,16 +2769,12 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Byron C. Hall, Deputy Supreme Or-</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L746: isolated marker/symbol line :: 140</t>
+          <t>L739: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
@@ -3028,16 +2808,12 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L473: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”One of the pieces to be played by</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L747: isolated marker/symbol line :: 139</t>
+          <t>L746: isolated marker/symbol line :: 140</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
@@ -3071,16 +2847,12 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: nel's parade." Whatâ€™s the use of the</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L753: isolated marker/symbol line :: 145</t>
+          <t>L747: isolated marker/symbol line :: 139</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
@@ -3114,16 +2886,12 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L479: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Hon. J. M. Gibson made as good a run</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L754: isolated marker/symbol line :: 143</t>
+          <t>L753: isolated marker/symbol line :: 145</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
@@ -3157,16 +2925,12 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L485: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Andrew Fox, No. 55 Oxford street,</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L758: isolated marker/symbol line :: 78</t>
+          <t>L754: isolated marker/symbol line :: 143</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
@@ -3200,16 +2964,12 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L489: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ephâ€™s Hospital in a critical condition.</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L762: isolated marker/symbol line :: 149</t>
+          <t>L758: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
@@ -3243,16 +3003,12 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L491: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” A Chicago firm ol architects has</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L763: isolated marker/symbol line :: 148</t>
+          <t>L762: isolated marker/symbol line :: 149</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
@@ -3286,16 +3042,12 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”The Imperial Oil Company (limited)</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L768: isolated marker/symbol line :: 141</t>
+          <t>L763: isolated marker/symbol line :: 148</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
@@ -3329,16 +3081,12 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L505: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”This has been a busy day in the City</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L769: isolated marker/symbol line :: 142</t>
+          <t>L768: isolated marker/symbol line :: 141</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
@@ -3372,16 +3120,12 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Treasurerâ€™s office. All city officials,</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L774: isolated marker/symbol line :: 118</t>
+          <t>L769: isolated marker/symbol line :: 142</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
@@ -3415,16 +3159,12 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L512: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -â€”The vocal and instrumental recital</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L779: isolated marker/symbol line :: 101</t>
+          <t>L774: isolated marker/symbol line :: 118</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
@@ -3458,16 +3198,12 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L519: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Mr. William Robinson, of No. 124</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L780: isolated marker/symbol line :: 100</t>
+          <t>L779: isolated marker/symbol line :: 101</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
@@ -3501,16 +3237,12 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L526: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”The Beach is beginning to assume a</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L784: isolated marker/symbol line :: 124</t>
+          <t>L780: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
@@ -3544,16 +3276,12 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L528: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: soon be erected clear up to Dynesâ€™. The</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L785: isolated marker/symbol line :: 122</t>
+          <t>L784: isolated marker/symbol line :: 124</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
@@ -3564,7 +3292,7 @@
       <c r="P58" s="1" t="inlineStr"/>
       <c r="Q58" s="1" t="inlineStr">
         <is>
-          <t>L1413: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT | punctuation artifact: repeated periods :: BarrÃ´wmore ... ...Father Point.Liverpool</t>
+          <t>L1413: punctuation artifact: repeated periods :: Barrôwmore ... ...Father Point.Liverpool</t>
         </is>
       </c>
       <c r="R58" s="1" t="inlineStr"/>
@@ -3587,16 +3315,12 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L563: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pany and all concerned,â€”We, the mem-</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L789: isolated marker/symbol line :: 125</t>
+          <t>L785: isolated marker/symbol line :: 122</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
@@ -3626,16 +3350,12 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L570: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Companyâ€™s cars, on Sabbath, during</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L790: isolated marker/symbol line :: 123</t>
+          <t>L789: isolated marker/symbol line :: 125</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
@@ -3665,16 +3385,12 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L583: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Porter-Grantâ€™s, Carlingâ€™s, Davies' India Pale,</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L796: isolated marker/symbol line :: 119</t>
+          <t>L790: isolated marker/symbol line :: 123</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
@@ -3704,16 +3420,12 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Labattâ€™s Ordinary and Labattâ€™s Stock, Davies'</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L797: symbol-only separator/garbage line :: 1 \$</t>
+          <t>L796: isolated marker/symbol line :: 119</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
@@ -3743,16 +3455,12 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L585: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Crystal, Daviesâ€™ White Label, Dowâ€™s pints and</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L801: isolated marker/symbol line :: 44</t>
+          <t>L797: symbol-only separator/garbage line :: 1 \$</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
@@ -3782,16 +3490,12 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: quarts, Ontario India Pale, Kuntzâ€™ Lager (or-</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L803: isolated marker/symbol line :: 109</t>
+          <t>L801: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
@@ -3821,16 +3525,12 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: dina y and export), Grantâ€™s Export, Bass' Ale</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: 138</t>
+          <t>L803: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
@@ -3860,16 +3560,12 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L588: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and Guinnessâ€™ Porter, Complete stock of Ginger</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L819: isolated marker/symbol line :: 127</t>
+          <t>L809: isolated marker/symbol line :: 138</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
@@ -3899,16 +3595,12 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L603: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: menâ€™s Meet and Prohibitionistsâ€™</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L820: isolated marker/symbol line :: 125</t>
+          <t>L819: isolated marker/symbol line :: 127</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
@@ -3938,16 +3630,12 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L631: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ERSKINEâ€™S PROTEST.</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L826: isolated marker/symbol line :: 160</t>
+          <t>L820: isolated marker/symbol line :: 125</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
@@ -3977,16 +3665,12 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: representative meeting of the congrÃ©ga-</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L832: isolated marker/symbol line :: 115</t>
+          <t>L826: isolated marker/symbol line :: 160</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
@@ -4016,16 +3700,12 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ladiesâ€™ Aid Society and the Epworth</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L833: isolated marker/symbol line :: 112</t>
+          <t>L832: isolated marker/symbol line :: 115</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
@@ -4055,16 +3735,12 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L689: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Sir,â€”I do not know how many stayed</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L838: isolated marker/symbol line :: 160</t>
+          <t>L833: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
@@ -4094,16 +3770,12 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN :: 'â€¢ De Kovenâ€™s Nita Gitana" in a</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L844: isolated marker/symbol line :: 127</t>
+          <t>L838: isolated marker/symbol line :: 160</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
@@ -4133,16 +3805,12 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L771: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | abbreviation/spacing may be garbled :: â€¢5.30 and 900 p.m. A</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L845: isolated marker/symbol line :: 125</t>
+          <t>L844: isolated marker/symbol line :: 127</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
@@ -4172,16 +3840,12 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L776: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN :: â€¢Calls at Oakvilâ€™e.</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L851: isolated marker/symbol line :: 10</t>
+          <t>L845: isolated marker/symbol line :: 125</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
@@ -4211,16 +3875,12 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L798: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Galbreaithâ€™s Block.</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L860: isolated marker/symbol line :: 100</t>
+          <t>L851: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
@@ -4250,16 +3910,12 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L827: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: stand on either side of the fireplaceâ€”</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L852: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
@@ -4289,16 +3945,12 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L841: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: or two of the highly decorative Benares 2â€˜</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L865: isolated marker/symbol line :: .</t>
+          <t>L860: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
@@ -4328,16 +3980,12 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Eliza Clark at St. Jamesâ€™ Church, Dun-</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L866: isolated marker/symbol line :: .</t>
+          <t>L864: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
@@ -4367,16 +4015,12 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L873: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: urday at Paine &amp; Buckeâ€™s. Read this</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L870: isolated marker/symbol line :: 127</t>
+          <t>L865: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
@@ -4406,16 +4050,12 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
       <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L884: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: yard.â€”Paine &amp; Bucke, the dress goods</t>
-        </is>
-      </c>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L878: isolated marker/symbol line :: 75</t>
+          <t>L866: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -4441,16 +4081,12 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
       <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L892: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: at 2.30 p. m., in Queenâ€™s Hall, on</t>
-        </is>
-      </c>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L879: isolated marker/symbol line :: A</t>
+          <t>L870: isolated marker/symbol line :: 127</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -4476,16 +4112,12 @@
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr"/>
       <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L905: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 181 tons nutâ€”all best Scranton, 441 tons Rey-</t>
-        </is>
-      </c>
+      <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L884: isolated marker/symbol line :: 118</t>
+          <t>L878: isolated marker/symbol line :: 75</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -4511,16 +4143,12 @@
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr"/>
       <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L952: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: ployees in the building withâ€˜a cook-</t>
-        </is>
-      </c>
+      <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L891: isolated marker/symbol line :: 128</t>
+          <t>L879: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -4546,16 +4174,12 @@
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr"/>
       <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L955: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”John Hennessy and Herman Koskey,</t>
-        </is>
-      </c>
+      <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L899: isolated marker/symbol line :: 150</t>
+          <t>L884: isolated marker/symbol line :: 118</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4581,16 +4205,12 @@
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr"/>
       <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L964: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”A foundationless report appeared in</t>
-        </is>
-      </c>
+      <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L905: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L891: isolated marker/symbol line :: 128</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4616,16 +4236,12 @@
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr"/>
       <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”At Osgoode Hall yesterday Mr. P. D.</t>
-        </is>
-      </c>
+      <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L899: isolated marker/symbol line :: 150</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4651,16 +4267,12 @@
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr"/>
       <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L1017: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: II.â€”Picton street, from Ferguson avenue to</t>
-        </is>
-      </c>
+      <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L915: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L905: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4686,16 +4298,12 @@
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr"/>
       <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L1021: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: seen at the City Engineerâ€™s office, where forms</t>
-        </is>
-      </c>
+      <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L923: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L914: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4721,16 +4329,12 @@
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr"/>
       <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L1175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Farmersâ€™ L. &amp; Svs..........</t>
-        </is>
-      </c>
+      <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L924: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L915: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4756,16 +4360,12 @@
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr"/>
       <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L1313: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: street cast, opposite Ladiesâ€™ College.</t>
-        </is>
-      </c>
+      <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L930: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L923: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4791,16 +4391,12 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr"/>
       <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L1368: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: found in Priestleyâ€™s famous dress fab-</t>
-        </is>
-      </c>
+      <c r="K91" s="1" t="inlineStr"/>
       <c r="L91" s="1" t="inlineStr"/>
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L931: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L924: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4826,16 +4422,12 @@
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr"/>
       <c r="J92" s="1" t="inlineStr"/>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L1413: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT | punctuation artifact: repeated periods :: BarrÃ´wmore ... ...Father Point.Liverpool</t>
-        </is>
-      </c>
+      <c r="K92" s="1" t="inlineStr"/>
       <c r="L92" s="1" t="inlineStr"/>
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L942: isolated marker/symbol line :: 0</t>
+          <t>L930: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -4861,14 +4453,14 @@
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr"/>
       <c r="J93" s="1" t="inlineStr"/>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L1415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ BAILIFF'S SALE.</t>
-        </is>
-      </c>
+      <c r="K93" s="1" t="inlineStr"/>
       <c r="L93" s="1" t="inlineStr"/>
       <c r="M93" s="1" t="inlineStr"/>
-      <c r="N93" s="1" t="inlineStr"/>
+      <c r="N93" s="1" t="inlineStr">
+        <is>
+          <t>L931: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
       <c r="O93" s="1" t="inlineStr"/>
       <c r="P93" s="1" t="inlineStr"/>
       <c r="Q93" s="1" t="inlineStr"/>
@@ -4892,14 +4484,14 @@
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr"/>
       <c r="J94" s="1" t="inlineStr"/>
-      <c r="K94" s="1" t="inlineStr">
-        <is>
-          <t>L1420: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: at 10 oâ€™clock, the following goods : Bed-</t>
-        </is>
-      </c>
+      <c r="K94" s="1" t="inlineStr"/>
       <c r="L94" s="1" t="inlineStr"/>
       <c r="M94" s="1" t="inlineStr"/>
-      <c r="N94" s="1" t="inlineStr"/>
+      <c r="N94" s="1" t="inlineStr">
+        <is>
+          <t>L942: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O94" s="1" t="inlineStr"/>
       <c r="P94" s="1" t="inlineStr"/>
       <c r="Q94" s="1" t="inlineStr"/>
@@ -4912,130 +4504,6 @@
       <c r="X94" s="1" t="inlineStr"/>
       <c r="Y94" s="1" t="inlineStr"/>
     </row>
-    <row r="95">
-      <c r="A95" s="1" t="inlineStr"/>
-      <c r="B95" s="1" t="inlineStr"/>
-      <c r="C95" s="1" t="inlineStr"/>
-      <c r="D95" s="1" t="inlineStr"/>
-      <c r="E95" s="1" t="inlineStr"/>
-      <c r="F95" s="1" t="inlineStr"/>
-      <c r="G95" s="1" t="inlineStr"/>
-      <c r="H95" s="1" t="inlineStr"/>
-      <c r="I95" s="1" t="inlineStr"/>
-      <c r="J95" s="1" t="inlineStr"/>
-      <c r="K95" s="1" t="inlineStr">
-        <is>
-          <t>L1431: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: was held at Mrs. Tildenâ€™s beautiful</t>
-        </is>
-      </c>
-      <c r="L95" s="1" t="inlineStr"/>
-      <c r="M95" s="1" t="inlineStr"/>
-      <c r="N95" s="1" t="inlineStr"/>
-      <c r="O95" s="1" t="inlineStr"/>
-      <c r="P95" s="1" t="inlineStr"/>
-      <c r="Q95" s="1" t="inlineStr"/>
-      <c r="R95" s="1" t="inlineStr"/>
-      <c r="S95" s="1" t="inlineStr"/>
-      <c r="T95" s="1" t="inlineStr"/>
-      <c r="U95" s="1" t="inlineStr"/>
-      <c r="V95" s="1" t="inlineStr"/>
-      <c r="W95" s="1" t="inlineStr"/>
-      <c r="X95" s="1" t="inlineStr"/>
-      <c r="Y95" s="1" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="inlineStr"/>
-      <c r="B96" s="1" t="inlineStr"/>
-      <c r="C96" s="1" t="inlineStr"/>
-      <c r="D96" s="1" t="inlineStr"/>
-      <c r="E96" s="1" t="inlineStr"/>
-      <c r="F96" s="1" t="inlineStr"/>
-      <c r="G96" s="1" t="inlineStr"/>
-      <c r="H96" s="1" t="inlineStr"/>
-      <c r="I96" s="1" t="inlineStr"/>
-      <c r="J96" s="1" t="inlineStr"/>
-      <c r="K96" s="1" t="inlineStr">
-        <is>
-          <t>L1433: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of the Ladiesâ€™ Aid of Emerald Street</t>
-        </is>
-      </c>
-      <c r="L96" s="1" t="inlineStr"/>
-      <c r="M96" s="1" t="inlineStr"/>
-      <c r="N96" s="1" t="inlineStr"/>
-      <c r="O96" s="1" t="inlineStr"/>
-      <c r="P96" s="1" t="inlineStr"/>
-      <c r="Q96" s="1" t="inlineStr"/>
-      <c r="R96" s="1" t="inlineStr"/>
-      <c r="S96" s="1" t="inlineStr"/>
-      <c r="T96" s="1" t="inlineStr"/>
-      <c r="U96" s="1" t="inlineStr"/>
-      <c r="V96" s="1" t="inlineStr"/>
-      <c r="W96" s="1" t="inlineStr"/>
-      <c r="X96" s="1" t="inlineStr"/>
-      <c r="Y96" s="1" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="inlineStr"/>
-      <c r="B97" s="1" t="inlineStr"/>
-      <c r="C97" s="1" t="inlineStr"/>
-      <c r="D97" s="1" t="inlineStr"/>
-      <c r="E97" s="1" t="inlineStr"/>
-      <c r="F97" s="1" t="inlineStr"/>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
-      <c r="I97" s="1" t="inlineStr"/>
-      <c r="J97" s="1" t="inlineStr"/>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>L1444: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: 132 King st. east.â€”â€˜Phone 835.</t>
-        </is>
-      </c>
-      <c r="L97" s="1" t="inlineStr"/>
-      <c r="M97" s="1" t="inlineStr"/>
-      <c r="N97" s="1" t="inlineStr"/>
-      <c r="O97" s="1" t="inlineStr"/>
-      <c r="P97" s="1" t="inlineStr"/>
-      <c r="Q97" s="1" t="inlineStr"/>
-      <c r="R97" s="1" t="inlineStr"/>
-      <c r="S97" s="1" t="inlineStr"/>
-      <c r="T97" s="1" t="inlineStr"/>
-      <c r="U97" s="1" t="inlineStr"/>
-      <c r="V97" s="1" t="inlineStr"/>
-      <c r="W97" s="1" t="inlineStr"/>
-      <c r="X97" s="1" t="inlineStr"/>
-      <c r="Y97" s="1" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="inlineStr"/>
-      <c r="B98" s="1" t="inlineStr"/>
-      <c r="C98" s="1" t="inlineStr"/>
-      <c r="D98" s="1" t="inlineStr"/>
-      <c r="E98" s="1" t="inlineStr"/>
-      <c r="F98" s="1" t="inlineStr"/>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
-      <c r="I98" s="1" t="inlineStr"/>
-      <c r="J98" s="1" t="inlineStr"/>
-      <c r="K98" s="1" t="inlineStr">
-        <is>
-          <t>L1475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: going on at Kingsleyâ€™s. Hundreds</t>
-        </is>
-      </c>
-      <c r="L98" s="1" t="inlineStr"/>
-      <c r="M98" s="1" t="inlineStr"/>
-      <c r="N98" s="1" t="inlineStr"/>
-      <c r="O98" s="1" t="inlineStr"/>
-      <c r="P98" s="1" t="inlineStr"/>
-      <c r="Q98" s="1" t="inlineStr"/>
-      <c r="R98" s="1" t="inlineStr"/>
-      <c r="S98" s="1" t="inlineStr"/>
-      <c r="T98" s="1" t="inlineStr"/>
-      <c r="U98" s="1" t="inlineStr"/>
-      <c r="V98" s="1" t="inlineStr"/>
-      <c r="W98" s="1" t="inlineStr"/>
-      <c r="X98" s="1" t="inlineStr"/>
-      <c r="Y98" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
